--- a/public/templates/000_pm_suite/02_프로젝트 개발/04_설계/01_기획설계/프로젝트명_정보구조도(IA)_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/02_프로젝트 개발/04_설계/01_기획설계/프로젝트명_정보구조도(IA)_V1.0_20230530.xlsx
@@ -2736,12 +2736,12 @@
     <row r="12" ht="20.25" customHeight="1" s="206">
       <c r="B12" s="76" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI</t>
+          <t>한빛글로벌 SyncFlow AI</t>
         </is>
       </c>
       <c r="C12" s="160" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="207" t="n"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="D4" s="84" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" s="85" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D5" s="89" t="inlineStr">
         <is>
-          <t>SyncGuard AI 통합 웹 콘솔(Client/fe :3104, 심의·검토 워크스페이스 및 백오피스 통합) 및 마케팅허브 의뢰·결과(HTML/JSON) 연계 구조 반영</t>
+          <t>SyncFlow AI 통합 웹 콘솔(Client/fe :3104, 검증·검토 워크스페이스 및 백오피스 통합) 및 전자구매포털 의뢰·결과(HTML/JSON) 연계 구조 반영</t>
         </is>
       </c>
       <c r="E5" s="90" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B9" s="104" t="inlineStr">
         <is>
-          <t>마케팅허브 임베디드 브릿지 뷰</t>
+          <t>전자구매포털 임베디드 브릿지 뷰</t>
         </is>
       </c>
       <c r="C9" s="104" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G9" s="105" t="inlineStr">
         <is>
-          <t>마케팅허브 심의 의뢰 인바운드 연동 및 통합 웹 콘솔(Client/fe :3104) 시안·동영상(300MB 직접 업로드) Side-by-Side 대조 뷰어 진입</t>
+          <t>전자구매포털 검증 요청 인바운드 연동 및 통합 웹 콘솔(Client/fe :3104) 계약·도서·설계도면(300MB 직접 업로드) Side-by-Side 대조 뷰어 진입</t>
         </is>
       </c>
       <c r="H9" s="135" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G11" s="105" t="inlineStr">
         <is>
-          <t>대시보드 / 광고심의 / RA전문심의 / 이력조회 / 규제·실증 / 시스템관리</t>
+          <t>대시보드 / 계약·규격검증 / QA전문검증 / 이력조회 / 규제·시험검증 / 시스템관리</t>
         </is>
       </c>
       <c r="H11" s="135" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G12" s="105" t="inlineStr">
         <is>
-          <t>AI 1차 판정 완료, 실증 요청, RA 심의 완료 실시간 인앱 알림</t>
+          <t>AI 1차 판정 완료, 시험검증 요청, QA 검증 완료 실시간 인앱 알림</t>
         </is>
       </c>
       <c r="H12" s="135" t="n">
@@ -3754,7 +3754,7 @@
     <row r="15">
       <c r="A15" s="109" t="inlineStr">
         <is>
-          <t>F심의TER</t>
+          <t>F검증TER</t>
         </is>
       </c>
       <c r="B15" s="110" t="n"/>
@@ -3787,7 +3787,7 @@
     <row r="16">
       <c r="A16" s="103" t="inlineStr">
         <is>
-          <t>F심의TER</t>
+          <t>F검증TER</t>
         </is>
       </c>
       <c r="B16" s="104" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="27">
       <c r="A27" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B27" s="104" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C27" s="104" t="inlineStr">
         <is>
-          <t>종합 심의 관제 대시보드</t>
+          <t>종합 검증 관제 대시보드</t>
         </is>
       </c>
       <c r="D27" s="104" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G27" s="105" t="inlineStr">
         <is>
-          <t>개인/브랜드별 심의 진행 현황 및 위험도 통계</t>
+          <t>개인/사업부별 검증 진행 현황 및 위험도 통계</t>
         </is>
       </c>
       <c r="H27" s="135" t="n">
@@ -4164,17 +4164,17 @@
     <row r="28">
       <c r="A28" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B28" s="104" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="C28" s="104" t="inlineStr">
         <is>
-          <t>시안 및 동영상 업로드</t>
+          <t>계약·도서 및 설계도면 업로드</t>
         </is>
       </c>
       <c r="D28" s="104" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="G28" s="105" t="inlineStr">
         <is>
-          <t>PPTX/PDF/긴JPG 업로드 및 마케팅허브 의뢰건 자동 수신 확인</t>
+          <t>PPTX/PDF/긴JPG 업로드 및 전자구매포털 의뢰건 자동 수신 확인</t>
         </is>
       </c>
       <c r="H28" s="135" t="n">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="K28" s="119" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="L28" s="112" t="inlineStr">
@@ -4246,17 +4246,17 @@
     <row r="29">
       <c r="A29" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B29" s="104" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="C29" s="104" t="inlineStr">
         <is>
-          <t>동영상 사용자 지정 장면 캡처</t>
+          <t>CAD/PDF 설계도면 규격영역 스냅샷 추출</t>
         </is>
       </c>
       <c r="D29" s="104" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G29" s="105" t="inlineStr">
         <is>
-          <t>MP4 영상 재생 중 심의할 다중 장면을 사용자가 직접 캡처·저장 후 일괄 심의</t>
+          <t>CAD 설계도면 재생 중 검증할 다중 장면을 사용자가 직접 스냅샷·저장 후 일괄 검증</t>
         </is>
       </c>
       <c r="H29" s="135" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="K29" s="119" t="inlineStr">
         <is>
-          <t>SCR_CLM_01_V</t>
+          <t>SCR_REV_01_V</t>
         </is>
       </c>
       <c r="L29" s="112" t="inlineStr">
@@ -4328,12 +4328,12 @@
     <row r="30">
       <c r="A30" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B30" s="104" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="C30" s="104" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="G30" s="105" t="inlineStr">
         <is>
-          <t>표현사전·전성분 룰 ➔ 식약처 법령·ProductLab 실증 RAG ➔ 비학습 LLM 판정</t>
+          <t>표현사전·자재BOM 룰 ➔ 공정위·표준원 법령·PLM-Nexus 시험검증 RAG ➔ 비학습 LLM 판정</t>
         </is>
       </c>
       <c r="H30" s="135" t="n">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="K30" s="119" t="inlineStr">
         <is>
-          <t>SCR_CLM_02</t>
+          <t>SCR_REV_02</t>
         </is>
       </c>
       <c r="L30" s="112" t="inlineStr">
@@ -4410,17 +4410,17 @@
     <row r="31">
       <c r="A31" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B31" s="104" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="C31" s="104" t="inlineStr">
         <is>
-          <t>Side-by-Side 대조 및 대체어 치환</t>
+          <t>Side-by-Side 대조 및 표준대안 치환</t>
         </is>
       </c>
       <c r="D31" s="104" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G31" s="105" t="inlineStr">
         <is>
-          <t>시안/캡처장면 바운딩박스 하이라이트 동기화 및 법적 안전 대체문안 채택</t>
+          <t>계약·도서/스냅샷장면 바운딩박스 하이라이트 동기화 및 법적 안전 표준수정조항 채택</t>
         </is>
       </c>
       <c r="H31" s="135" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K31" s="119" t="inlineStr">
         <is>
-          <t>SCR_CLM_03</t>
+          <t>SCR_REV_03</t>
         </is>
       </c>
       <c r="L31" s="112" t="inlineStr">
@@ -4492,17 +4492,17 @@
     <row r="32">
       <c r="A32" s="103" t="inlineStr">
         <is>
-          <t>광고심의 (FO)</t>
+          <t>계약·규격검증 (FO)</t>
         </is>
       </c>
       <c r="B32" s="104" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="C32" s="104" t="inlineStr">
         <is>
-          <t>실증자료 매핑 및 소명 메모</t>
+          <t>시험성적서 매핑 및 소명 메모</t>
         </is>
       </c>
       <c r="D32" s="104" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="G32" s="105" t="inlineStr">
         <is>
-          <t>ProductLab 인체적용시험·효능 성적서 연결 및 연구원 실증 확인</t>
+          <t>PLM-Nexus 공인신뢰성시험·성능규격 성적서 연결 및 연구원 시험검증 확인</t>
         </is>
       </c>
       <c r="H32" s="135" t="n">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="K32" s="119" t="inlineStr">
         <is>
-          <t>SCR_CLM_04</t>
+          <t>SCR_REV_04</t>
         </is>
       </c>
       <c r="L32" s="112" t="inlineStr">
@@ -4574,17 +4574,17 @@
     <row r="33">
       <c r="A33" s="103" t="inlineStr">
         <is>
-          <t>RA 전문심의 (FO)</t>
+          <t>법무·QA 전문검토 (FO)</t>
         </is>
       </c>
       <c r="B33" s="104" t="inlineStr">
         <is>
-          <t>심의 접수 대기</t>
+          <t>검증 접수 대기</t>
         </is>
       </c>
       <c r="C33" s="104" t="inlineStr">
         <is>
-          <t>RA 심의 접수 목록 그리드</t>
+          <t>QA 검증 접수 목록 그리드</t>
         </is>
       </c>
       <c r="D33" s="104" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="G33" s="105" t="inlineStr">
         <is>
-          <t>긴급도/위험도 필터링 및 담당 RA 배정</t>
+          <t>긴급도/위험도 필터링 및 담당 검토역 배정</t>
         </is>
       </c>
       <c r="H33" s="135" t="n">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="K33" s="119" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="L33" s="112" t="inlineStr">
@@ -4656,17 +4656,17 @@
     <row r="34">
       <c r="A34" s="103" t="inlineStr">
         <is>
-          <t>RA 전문심의 (FO)</t>
+          <t>법무·QA 전문검토 (FO)</t>
         </is>
       </c>
       <c r="B34" s="104" t="inlineStr">
         <is>
-          <t>전문 심의 판정</t>
+          <t>전문 검증 판정</t>
         </is>
       </c>
       <c r="C34" s="104" t="inlineStr">
         <is>
-          <t>RA 판정 및 원클릭 피드백 콘솔</t>
+          <t>법무·QA 판정 및 원클릭 피드백 콘솔</t>
         </is>
       </c>
       <c r="D34" s="104" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="G34" s="105" t="inlineStr">
         <is>
-          <t>AI 판정 오버라이드, 최종 의견 작성, 승인/반려 확정 및 마케팅허브 회신</t>
+          <t>AI 판정 오버라이드, 최종 의견 작성, 승인/반려 확정 및 전자구매포털 회신</t>
         </is>
       </c>
       <c r="H34" s="135" t="n">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="K34" s="119" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="L34" s="112" t="inlineStr">
@@ -4738,17 +4738,17 @@
     <row r="35">
       <c r="A35" s="103" t="inlineStr">
         <is>
-          <t>RA 전문심의 (FO)</t>
+          <t>법무·QA 전문검토 (FO)</t>
         </is>
       </c>
       <c r="B35" s="104" t="inlineStr">
         <is>
-          <t>심의 확정 리포트</t>
+          <t>검증 확정 리포트</t>
         </is>
       </c>
       <c r="C35" s="104" t="inlineStr">
         <is>
-          <t>심의 결과 리포트(PDF/Word) 출력</t>
+          <t>검증 결과 리포트(PDF/Word) 출력</t>
         </is>
       </c>
       <c r="D35" s="104" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="G35" s="105" t="inlineStr">
         <is>
-          <t>문장/장면별 판정·법령근거·대체문안 종합 리포트 다운로드</t>
+          <t>문장/장면별 판정·법령근거·표준수정조항 종합 리포트 다운로드</t>
         </is>
       </c>
       <c r="H35" s="135" t="n">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="K35" s="119" t="inlineStr">
         <is>
-          <t>SCR_RA_03</t>
+          <t>SCR_QAL_03</t>
         </is>
       </c>
       <c r="L35" s="112" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="B36" s="104" t="inlineStr">
         <is>
-          <t>심의 이력 목록</t>
+          <t>검증 이력 목록</t>
         </is>
       </c>
       <c r="C36" s="104" t="inlineStr">
         <is>
-          <t>전체 심의 이력 다차원 검색</t>
+          <t>전체 검증 이력 다차원 검색</t>
         </is>
       </c>
       <c r="D36" s="104" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G36" s="105" t="inlineStr">
         <is>
-          <t>브랜드/제품/키워드/시맨틱 유사 판정 사례 검색</t>
+          <t>사업본부/제품/키워드/시맨틱 유사 판정 사례 검색</t>
         </is>
       </c>
       <c r="H36" s="135" t="n">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C37" s="104" t="inlineStr">
         <is>
-          <t>시안 버전별 문안 변경 비교 뷰어</t>
+          <t>계약·도서 버전별 계약조항 변경 비교 뷰어</t>
         </is>
       </c>
       <c r="D37" s="104" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G37" s="105" t="inlineStr">
         <is>
-          <t>수정 전·후 시안 문구 및 판정 등급 변화 비교</t>
+          <t>수정 전·후 계약·도서 조항 및 판정 등급 변화 비교</t>
         </is>
       </c>
       <c r="H37" s="135" t="n">
@@ -5577,7 +5577,7 @@
     <row r="67">
       <c r="A67" s="103" t="inlineStr">
         <is>
-          <t>규제·실증관리 (BO)</t>
+          <t>규제·시험검증관리 (BO)</t>
         </is>
       </c>
       <c r="B67" s="104" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C67" s="104" t="inlineStr">
         <is>
-          <t>표시광고 금지/주의 표현사전 관리</t>
+          <t>계약·기술규격 금지/주의 표현사전 관리</t>
         </is>
       </c>
       <c r="D67" s="104" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G67" s="105" t="inlineStr">
         <is>
-          <t>식약처 가이드라인·자주 틀리는 사례 기반 규칙 등록/엑셀 업로드</t>
+          <t>공정위·표준원 가이드라인·자주 틀리는 사례 기반 규칙 등록/엑셀 업로드</t>
         </is>
       </c>
       <c r="H67" s="135" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="K67" s="119" t="inlineStr">
         <is>
-          <t>SCR_REG_01</t>
+          <t>SCR_STD_01</t>
         </is>
       </c>
       <c r="L67" s="112" t="inlineStr">
@@ -5659,17 +5659,17 @@
     <row r="68">
       <c r="A68" s="103" t="inlineStr">
         <is>
-          <t>규제·실증관리 (BO)</t>
+          <t>규제·시험검증관리 (BO)</t>
         </is>
       </c>
       <c r="B68" s="104" t="inlineStr">
         <is>
-          <t>법령·처분사례 RAG</t>
+          <t>법령·심결사례 RAG</t>
         </is>
       </c>
       <c r="C68" s="104" t="inlineStr">
         <is>
-          <t>법령·행정처분 수집 및 지능형 Diff 색인</t>
+          <t>법령·시정명령·심결 수집 및 지능형 Diff 색인</t>
         </is>
       </c>
       <c r="D68" s="104" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="G68" s="105" t="inlineStr">
         <is>
-          <t>국가법령·식약처 처분사례 크롤링, 기존 조항과 지능형 비교 후 변경분 재임베딩</t>
+          <t>국가법령·공정위·표준원 심결사례 크롤링, 기존 조항과 지능형 비교 후 변경분 재임베딩</t>
         </is>
       </c>
       <c r="H68" s="135" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="K68" s="119" t="inlineStr">
         <is>
-          <t>SCR_REG_02</t>
+          <t>SCR_STD_02</t>
         </is>
       </c>
       <c r="L68" s="112" t="inlineStr">
@@ -5741,17 +5741,17 @@
     <row r="69">
       <c r="A69" s="103" t="inlineStr">
         <is>
-          <t>규제·실증관리 (BO)</t>
+          <t>규제·시험검증관리 (BO)</t>
         </is>
       </c>
       <c r="B69" s="104" t="inlineStr">
         <is>
-          <t>전성분·실증 연계</t>
+          <t>자재BOM·시험검증 연계</t>
         </is>
       </c>
       <c r="C69" s="104" t="inlineStr">
         <is>
-          <t>전성분 배합한도 및 ProductLab 실증 조회</t>
+          <t>자재BOM 유해물질한도 및 PLM-Nexus 시험검증 조회</t>
         </is>
       </c>
       <c r="D69" s="104" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G69" s="105" t="inlineStr">
         <is>
-          <t>사내 전성분 RDB·ProductLab 실증데이터 조회 ([Option] KT레몬 벡터 검색 연동)</t>
+          <t>사내 자재BOM RDB·PLM-Nexus 시험검증데이터 조회 ([Option] HB-Monitor 벡터 검색 연동)</t>
         </is>
       </c>
       <c r="H69" s="135" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K69" s="119" t="inlineStr">
         <is>
-          <t>SCR_REG_03</t>
+          <t>SCR_STD_03</t>
         </is>
       </c>
       <c r="L69" s="112" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="G70" s="105" t="inlineStr">
         <is>
-          <t>마케터/연구원/RA/관리자 역할 매핑 및 접근 통제</t>
+          <t>구매담당/품질연구원/법무QA/관리자 역할 매핑 및 접근 통제</t>
         </is>
       </c>
       <c r="H70" s="135" t="n">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C72" s="104" t="inlineStr">
         <is>
-          <t>마케팅허브/프로덕트랩/SSO/[Option]레몬 관제</t>
+          <t>전자구매포털/피엘엠넥서스/SSO/[Option]통합관제(HB-Monitor)</t>
         </is>
       </c>
       <c r="D72" s="104" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="G3" s="239" t="inlineStr">
         <is>
-          <t>마케터</t>
+          <t>구매담당자</t>
         </is>
       </c>
       <c r="H3" s="239" t="inlineStr">
         <is>
-          <t>RA전문가</t>
+          <t>법무·QA전문위원</t>
         </is>
       </c>
       <c r="I3" s="239" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="F4" s="240" t="inlineStr">
         <is>
-          <t>종합 심의 관제 대시보드</t>
+          <t>종합 검증 관제 대시보드</t>
         </is>
       </c>
       <c r="G4" s="239" t="inlineStr">
@@ -6968,39 +6968,39 @@
       </c>
       <c r="J4" s="240" t="inlineStr">
         <is>
-          <t>개인별 심의 현황 및 KPI 통계</t>
+          <t>개인별 검증 현황 및 KPI 통계</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="239" t="inlineStr">
         <is>
-          <t>MNU_CLM_01</t>
+          <t>MNU_REV_01</t>
         </is>
       </c>
       <c r="B5" s="240" t="inlineStr">
         <is>
-          <t>광고심의</t>
+          <t>계약·규격검증</t>
         </is>
       </c>
       <c r="C5" s="240" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="D5" s="239" t="inlineStr">
         <is>
-          <t>시안 등록</t>
+          <t>계약·도서 등록</t>
         </is>
       </c>
       <c r="E5" s="239" t="inlineStr">
         <is>
-          <t>SCR_CLM_01</t>
+          <t>SCR_REV_01</t>
         </is>
       </c>
       <c r="F5" s="240" t="inlineStr">
         <is>
-          <t>심의 의뢰 등록 및 시안·동영상 장면 캡처</t>
+          <t>검증 요청 등록 및 계약·도서·설계도면 스냅샷 추출</t>
         </is>
       </c>
       <c r="G5" s="239" t="inlineStr">
@@ -7020,24 +7020,24 @@
       </c>
       <c r="J5" s="240" t="inlineStr">
         <is>
-          <t>PPTX/PDF/긴JPG 첨부 및 동영상 사용자 지정 장면 캡처·저장</t>
+          <t>PPTX/PDF/긴JPG 첨부 및 CAD/PDF 설계도면 규격영역 스냅샷 추출·저장</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="239" t="inlineStr">
         <is>
-          <t>MNU_CLM_02</t>
+          <t>MNU_REV_02</t>
         </is>
       </c>
       <c r="B6" s="240" t="inlineStr">
         <is>
-          <t>광고심의</t>
+          <t>계약·규격검증</t>
         </is>
       </c>
       <c r="C6" s="240" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="D6" s="239" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="E6" s="239" t="inlineStr">
         <is>
-          <t>SCR_CLM_02</t>
+          <t>SCR_REV_02</t>
         </is>
       </c>
       <c r="F6" s="240" t="inlineStr">
@@ -7079,32 +7079,32 @@
     <row r="7">
       <c r="A7" s="239" t="inlineStr">
         <is>
-          <t>MNU_CLM_03</t>
+          <t>MNU_REV_03</t>
         </is>
       </c>
       <c r="B7" s="240" t="inlineStr">
         <is>
-          <t>광고심의</t>
+          <t>계약·규격검증</t>
         </is>
       </c>
       <c r="C7" s="240" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="D7" s="239" t="inlineStr">
         <is>
-          <t>문안 대조/수정</t>
+          <t>조항 대조/수정</t>
         </is>
       </c>
       <c r="E7" s="239" t="inlineStr">
         <is>
-          <t>SCR_CLM_03</t>
+          <t>SCR_REV_03</t>
         </is>
       </c>
       <c r="F7" s="240" t="inlineStr">
         <is>
-          <t>Side-by-Side 대조 및 대체어 치환</t>
+          <t>Side-by-Side 대조 및 표준대안 치환</t>
         </is>
       </c>
       <c r="G7" s="239" t="inlineStr">
@@ -7131,17 +7131,17 @@
     <row r="8">
       <c r="A8" s="239" t="inlineStr">
         <is>
-          <t>MNU_CLM_04</t>
+          <t>MNU_REV_04</t>
         </is>
       </c>
       <c r="B8" s="240" t="inlineStr">
         <is>
-          <t>광고심의</t>
+          <t>계약·규격검증</t>
         </is>
       </c>
       <c r="C8" s="240" t="inlineStr">
         <is>
-          <t>신규 심의 의뢰</t>
+          <t>신규 검증 요청</t>
         </is>
       </c>
       <c r="D8" s="239" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="E8" s="239" t="inlineStr">
         <is>
-          <t>SCR_CLM_04</t>
+          <t>SCR_REV_04</t>
         </is>
       </c>
       <c r="F8" s="240" t="inlineStr">
         <is>
-          <t>실증자료 매핑 및 소명 메모</t>
+          <t>시험성적서 매핑 및 소명 메모</t>
         </is>
       </c>
       <c r="G8" s="239" t="inlineStr">
@@ -7176,24 +7176,24 @@
       </c>
       <c r="J8" s="240" t="inlineStr">
         <is>
-          <t>ProductLab 시험성적서 연결</t>
+          <t>PLM-Nexus 시험성적서 연결</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="239" t="inlineStr">
         <is>
-          <t>MNU_RA_01</t>
+          <t>MNU_QA_01</t>
         </is>
       </c>
       <c r="B9" s="240" t="inlineStr">
         <is>
-          <t>RA 전문심의</t>
+          <t>법무·QA 전문검토</t>
         </is>
       </c>
       <c r="C9" s="240" t="inlineStr">
         <is>
-          <t>심의 접수 대기</t>
+          <t>검증 접수 대기</t>
         </is>
       </c>
       <c r="D9" s="239" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E9" s="239" t="inlineStr">
         <is>
-          <t>SCR_RA_01</t>
+          <t>SCR_QAL_01</t>
         </is>
       </c>
       <c r="F9" s="240" t="inlineStr">
         <is>
-          <t>RA 심의 접수 목록 그리드</t>
+          <t>QA 검증 접수 목록 그리드</t>
         </is>
       </c>
       <c r="G9" s="239" t="inlineStr">
@@ -7228,24 +7228,24 @@
       </c>
       <c r="J9" s="240" t="inlineStr">
         <is>
-          <t>긴급도/위험도 필터링 및 심의 배정</t>
+          <t>긴급도/위험도 필터링 및 검증 배정</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="239" t="inlineStr">
         <is>
-          <t>MNU_RA_02</t>
+          <t>MNU_QA_02</t>
         </is>
       </c>
       <c r="B10" s="240" t="inlineStr">
         <is>
-          <t>RA 전문심의</t>
+          <t>법무·QA 전문검토</t>
         </is>
       </c>
       <c r="C10" s="240" t="inlineStr">
         <is>
-          <t>전문 심의 판정</t>
+          <t>전문 검증 판정</t>
         </is>
       </c>
       <c r="D10" s="239" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="E10" s="239" t="inlineStr">
         <is>
-          <t>SCR_RA_02</t>
+          <t>SCR_QAL_02</t>
         </is>
       </c>
       <c r="F10" s="240" t="inlineStr">
         <is>
-          <t>RA 전문가 판정 및 오버라이드 콘솔</t>
+          <t>법무·QA 전문위원 판정 및 오버라이드 콘솔</t>
         </is>
       </c>
       <c r="G10" s="239" t="inlineStr">
@@ -7287,17 +7287,17 @@
     <row r="11">
       <c r="A11" s="239" t="inlineStr">
         <is>
-          <t>MNU_RA_03</t>
+          <t>MNU_QA_03</t>
         </is>
       </c>
       <c r="B11" s="240" t="inlineStr">
         <is>
-          <t>RA 전문심의</t>
+          <t>법무·QA 전문검토</t>
         </is>
       </c>
       <c r="C11" s="240" t="inlineStr">
         <is>
-          <t>심의 확정 리포트</t>
+          <t>검증 확정 리포트</t>
         </is>
       </c>
       <c r="D11" s="239" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="E11" s="239" t="inlineStr">
         <is>
-          <t>SCR_RA_03</t>
+          <t>SCR_QAL_03</t>
         </is>
       </c>
       <c r="F11" s="240" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="C12" s="240" t="inlineStr">
         <is>
-          <t>심의 이력 목록</t>
+          <t>검증 이력 목록</t>
         </is>
       </c>
       <c r="D12" s="239" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F12" s="240" t="inlineStr">
         <is>
-          <t>전체 심의 이력 조회 및 검색</t>
+          <t>전체 검증 이력 조회 및 검색</t>
         </is>
       </c>
       <c r="G12" s="239" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="J12" s="240" t="inlineStr">
         <is>
-          <t>브랜드/제품/일자별 다차원 검색</t>
+          <t>사업본부/제품/일자별 다차원 검색</t>
         </is>
       </c>
       <c r="M12" s="75" t="n"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="F13" s="240" t="inlineStr">
         <is>
-          <t>시안 버전별 문안 변경 이력 뷰어</t>
+          <t>계약·도서 버전별 계약조항 변경 이력 뷰어</t>
         </is>
       </c>
       <c r="G13" s="239" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="J14" s="240" t="inlineStr">
         <is>
-          <t>식약처 사후 소명용 무결성 이력</t>
+          <t>공정위·표준원 사후 소명용 무결성 이력</t>
         </is>
       </c>
     </row>
@@ -7516,12 +7516,12 @@
       </c>
       <c r="E15" s="239" t="inlineStr">
         <is>
-          <t>SCR_REG_01</t>
+          <t>SCR_STD_01</t>
         </is>
       </c>
       <c r="F15" s="240" t="inlineStr">
         <is>
-          <t>제품 표시·광고 금지/주의 룰 관리</t>
+          <t>구매계약·기술규격 금지/주의 룰 관리</t>
         </is>
       </c>
       <c r="G15" s="239" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="C16" s="240" t="inlineStr">
         <is>
-          <t>식약처 처분사례</t>
+          <t>공정위·표준원 심결사례</t>
         </is>
       </c>
       <c r="D16" s="239" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E16" s="239" t="inlineStr">
         <is>
-          <t>SCR_REG_02</t>
+          <t>SCR_STD_02</t>
         </is>
       </c>
       <c r="F16" s="240" t="inlineStr">
         <is>
-          <t>식약처 행정처분 판례 및 RAG 색인</t>
+          <t>공정위·표준원 하도급 심결례 및 RAG 색인</t>
         </is>
       </c>
       <c r="G16" s="239" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="C17" s="240" t="inlineStr">
         <is>
-          <t>전성분·실증 규제조회</t>
+          <t>자재BOM·시험검증 규제조회</t>
         </is>
       </c>
       <c r="D17" s="239" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="E17" s="239" t="inlineStr">
         <is>
-          <t>SCR_REG_03</t>
+          <t>SCR_STD_03</t>
         </is>
       </c>
       <c r="F17" s="240" t="inlineStr">
         <is>
-          <t>원료 전성분 배합한도 및 ProductLab 실증 조회</t>
+          <t>원소재 자재BOM 유해물질한도 및 PLM-Nexus 시험검증 조회</t>
         </is>
       </c>
       <c r="G17" s="239" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="J17" s="240" t="inlineStr">
         <is>
-          <t>전성분 RDB·ProductLab 실증 조회 ([Option] KT레몬 연동)</t>
+          <t>자재BOM RDB·PLM-Nexus 시험검증 조회 ([Option] HB-Monitor 연동)</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="J18" s="240" t="inlineStr">
         <is>
-          <t>마케터, RA, 관리자 권한 매핑</t>
+          <t>구매담당자, QA, 관리자 권한 매핑</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F20" s="240" t="inlineStr">
         <is>
-          <t>SSO/MarketingHub/ProductLab/[Option]레몬 연계 모니터링</t>
+          <t>SSO/SRM-Portal/PLM-Nexus/[Option]HB-Monitor 연계 모니터링</t>
         </is>
       </c>
       <c r="G20" s="239" t="inlineStr">
